--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_50305.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_50305.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lcizioiri</t>
+          <t>Iluck</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IRLLEID</t>
+          <t>RIKU</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G02G</t>
+          <t>G32C</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_50305.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_50305.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G32C</t>
+          <t>G02A</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_50305.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_50305.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Iluck</t>
+          <t>Ictok</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RIKU</t>
+          <t>PIEU</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>3345</v>
+        <v>379.5</v>
       </c>
       <c r="K4" t="n">
         <v>100001</v>
@@ -730,7 +730,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>94.2</v>
+        <v>91.2</v>
       </c>
       <c r="K7" t="n">
         <v>10</v>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_50305.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_50305.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ictok</t>
+          <t>ICTOK</t>
         </is>
       </c>
     </row>
@@ -705,9 +705,6 @@
       <c r="J4" t="n">
         <v>379.5</v>
       </c>
-      <c r="K4" t="n">
-        <v>100001</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -731,9 +728,6 @@
       </c>
       <c r="J7" t="n">
         <v>91.2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>10</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_50305.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_50305.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
